--- a/04_DESIGN_TABLES/DesignTable_6505.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_6505.xlsx
@@ -1953,24 +1953,58 @@
           <t>6505-12-08</t>
         </is>
       </c>
+      <c r="B25" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="C25" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.719</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.391</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>1/2</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr">
         <is>
           <t>6505-12-08</t>
         </is>
       </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>3/4-14 (A NPTF) x 3/4-16 (B UN/UNF-2B)</t>
+        </is>
+      </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING; 2026-10-09 (left out of batch 15, staged): L15@DRIVE: OMi Items row 2021 Overall Length = 2.09; L16@DRIVE: OMi Items row 2021 L 1 Size = 1.67; CHEX@HEX: OMi Items row 2021 Hex Flat = 1.125; C3HEX@HEX: OMi Items row 2021 Nut Hex 1 = 0.875; D1@BORE: OMi Items row 2021 Side 1 ID = 0.719; D@BORE: OMi Items row 2021 Side 2 ID = 0.391; THDMAJ_A@DRIVE: 3/4-14 -&gt; 1.05 (end library); THDMAJ_B@DRIVE: 3/4-16 -&gt; 0.75 (end library) [user 2026-09-25: OMi dims &gt; Air-Way; user 2026-10-08: no size from Brennan alone -&gt; OMi stands, ASSUMED]; pairing: OMi Overall Length = L15 (pipe tip to the swivel-nut face), L 1 = L16 (pipe tip to the seat), Hex Flat = body hex CHEX, Nut Hex 1 = swivel nut hex C3HEX, Side 1 / 2 ID = pipe / swivel bore - pairing READ from the built 6505-12-12 row (OMi 2.28 / 1.72 vs its Air-Way L15 2.26 / L16 1.70; the 2026-09-25 audit marks the 6505 length mapping "uncertain") - ASSUMPTION</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | RESOLVED 2026-10-09 (staged): this part's own sizes from OMi WebsitePartsInfo2026 Items row 2021 - ASSUMED (one source). It was held in batch 15 because the Brennan TFA catalog prints other values for it; under the 2026-10-08 ruling the catalog (= OMi's source) is evidence only and OMi stands. Catalog print for the record: TFA-p018-t01: TUBE O.D. 1/2, A NPTF 3/4-14, B SAE 37Deg 3/4-16, A DRILL 0.609, B DRILL 0.391, L LGTH 1.67, L5 LGTH 2.09, C1 HEX 0.875, C HEX 1.125</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">

--- a/04_DESIGN_TABLES/DesignTable_6505.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_6505.xlsx
@@ -512,10 +512,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="D3" t="n">
         <v>0.5</v>
@@ -554,12 +554,12 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Air-Way s101 only (double-pass 20 rows); D1 column printed "---" on most rows (no value) -&gt; cell left empty in table, MISSING for D1 on those rows; CHEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R2009 Hex Flat = 0.500 (table had 0.44) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
+          <t>Air-Way s101 only (double-pass 20 rows); D1 column printed "---" on most rows (no value) -&gt; cell left empty in table, MISSING for D1 on those rows; CHEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R2009 Hex Flat = 0.500 (table had 0.44) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L15@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2009 = 1.36 (table had 1.34) [user 2026-10-18 A19]; L16@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2009 = 1.01 (table had 1) [user 2026-10-18 A19]</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>D1: printed "---" on Air-Way (not applicable to this size) -&gt; cell empty</t>
+          <t>D1: printed "---" on Air-Way (not applicable to this size) -&gt; cell empty | A19 (user 2026-10-18, group 2 settled): L15@DRIVE 1.34 -&gt; OMi 1.36 (Items!L2009, M031) | A19 (user 2026-10-18, group 2 settled): L16@DRIVE 1 -&gt; OMi 1.01 (Items!P2009, M032)</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -580,10 +580,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="C4" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="D4" t="n">
         <v>0.5600000000000001</v>
@@ -622,12 +622,12 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Air-Way s101 only (double-pass 20 rows); D1 column printed "---" on most rows (no value) -&gt; cell left empty in table, MISSING for D1 on those rows</t>
+          <t>Air-Way s101 only (double-pass 20 rows); D1 column printed "---" on most rows (no value) -&gt; cell left empty in table, MISSING for D1 on those rows; L15@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2011 = 1.56 (table had 1.53) [user 2026-10-18 A19]; L16@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2011 = 1.21 (table had 1.19) [user 2026-10-18 A19]</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>D1: printed "---" on Air-Way (not applicable to this size) -&gt; cell empty</t>
+          <t>D1: printed "---" on Air-Way (not applicable to this size) -&gt; cell empty | A19 (user 2026-10-18, group 2 settled): L15@DRIVE 1.53 -&gt; OMi 1.56 (Items!L2011, M031) | A19 (user 2026-10-18, group 2 settled): L16@DRIVE 1.19 -&gt; OMi 1.21 (Items!P2011, M032)</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="C5" t="n">
         <v>1.26</v>
@@ -690,12 +690,12 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Air-Way s101 only (double-pass 20 rows); D1 column printed "---" on most rows (no value) -&gt; cell left empty in table, MISSING for D1 on those rows</t>
+          <t>Air-Way s101 only (double-pass 20 rows); D1 column printed "---" on most rows (no value) -&gt; cell left empty in table, MISSING for D1 on those rows; L15@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2012 = 1.64 (table had 1.63) [user 2026-10-18 A19]</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>D1: printed "---" on Air-Way (not applicable to this size) -&gt; cell empty</t>
+          <t>D1: printed "---" on Air-Way (not applicable to this size) -&gt; cell empty | A19 (user 2026-10-18, group 2 settled): L15@DRIVE 1.63 -&gt; OMi 1.64 (Items!L2012, M031)</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -716,10 +716,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="C6" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="D6" t="n">
         <v>0.5600000000000001</v>
@@ -761,7 +761,12 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Air-Way s101 only (double-pass 20 rows); D1 column printed "---" on most rows (no value) -&gt; cell left empty in table, MISSING for D1 on those rows</t>
+          <t>Air-Way s101 only (double-pass 20 rows); D1 column printed "---" on most rows (no value) -&gt; cell left empty in table, MISSING for D1 on those rows; L15@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2013 = 1.68 (table had 1.72) [user 2026-10-18 A19]; L16@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2013 = 1.30 (table had 1.34) [user 2026-10-18 A19]</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>A19 (user 2026-10-18, group 2 settled): L15@DRIVE 1.72 -&gt; OMi 1.68 (Items!L2013, M031) | A19 (user 2026-10-18, group 2 settled): L16@DRIVE 1.34 -&gt; OMi 1.30 (Items!P2013, M032)</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -782,10 +787,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.72</v>
+        <v>1.64</v>
       </c>
       <c r="C7" t="n">
-        <v>1.34</v>
+        <v>1.26</v>
       </c>
       <c r="D7" t="n">
         <v>0.75</v>
@@ -824,12 +829,12 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Air-Way s101 only (double-pass 20 rows); D1 column printed "---" on most rows (no value) -&gt; cell left empty in table, MISSING for D1 on those rows</t>
+          <t>Air-Way s101 only (double-pass 20 rows); D1 column printed "---" on most rows (no value) -&gt; cell left empty in table, MISSING for D1 on those rows; L15@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2015 = 1.64 (table had 1.72) [user 2026-10-18 A19]; L16@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2015 = 1.26 (table had 1.34) [user 2026-10-18 A19]</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>D1: printed "---" on Air-Way (not applicable to this size) -&gt; cell empty</t>
+          <t>D1: printed "---" on Air-Way (not applicable to this size) -&gt; cell empty | A19 (user 2026-10-18, group 2 settled): L15@DRIVE 1.72 -&gt; OMi 1.64 (Items!L2015, M031) | A19 (user 2026-10-18, group 2 settled): L16@DRIVE 1.34 -&gt; OMi 1.26 (Items!P2015, M032)</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -984,10 +989,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="C10" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="D10" t="n">
         <v>0.88</v>
@@ -1029,7 +1034,12 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Air-Way s101 only (double-pass 20 rows); D1 column printed "---" on most rows (no value) -&gt; cell left empty in table, MISSING for D1 on those rows</t>
+          <t>Air-Way s101 only (double-pass 20 rows); D1 column printed "---" on most rows (no value) -&gt; cell left empty in table, MISSING for D1 on those rows; L15@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2017 = 1.88 (table had 1.86) [user 2026-10-18 A19]; L16@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2017 = 1.51 (table had 1.48) [user 2026-10-18 A19]</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>A19 (user 2026-10-18, group 2 settled): L15@DRIVE 1.86 -&gt; OMi 1.88 (Items!L2017, M031) | A19 (user 2026-10-18, group 2 settled): L16@DRIVE 1.48 -&gt; OMi 1.51 (Items!P2017, M032)</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1050,10 +1060,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="C11" t="n">
-        <v>1.48</v>
+        <v>1.56</v>
       </c>
       <c r="D11" t="n">
         <v>0.88</v>
@@ -1092,12 +1102,12 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Air-Way s101 only (double-pass 20 rows); D1 column printed "---" on most rows (no value) -&gt; cell left empty in table, MISSING for D1 on those rows</t>
+          <t>Air-Way s101 only (double-pass 20 rows); D1 column printed "---" on most rows (no value) -&gt; cell left empty in table, MISSING for D1 on those rows; L15@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2018 = 1.98 (table had 1.9) [user 2026-10-18 A19]; L16@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2018 = 1.56 (table had 1.48) [user 2026-10-18 A19]</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>D1: printed "---" on Air-Way (not applicable to this size) -&gt; cell empty</t>
+          <t>D1: printed "---" on Air-Way (not applicable to this size) -&gt; cell empty | A19 (user 2026-10-18, group 2 settled): L15@DRIVE 1.9 -&gt; OMi 1.98 (Items!L2018, M031) | A19 (user 2026-10-18, group 2 settled): L16@DRIVE 1.48 -&gt; OMi 1.56 (Items!P2018, M032)</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1118,10 +1128,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.28</v>
+        <v>2.1</v>
       </c>
       <c r="C12" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="D12" t="n">
         <v>1</v>
@@ -1160,12 +1170,12 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Air-Way s101 only (double-pass 20 rows); D1 column printed "---" on most rows (no value) -&gt; cell left empty in table, MISSING for D1 on those rows; CHEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R2019 Hex Flat = 1.000 (table had 0.94) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
+          <t>Air-Way s101 only (double-pass 20 rows); D1 column printed "---" on most rows (no value) -&gt; cell left empty in table, MISSING for D1 on those rows; CHEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R2019 Hex Flat = 1.000 (table had 0.94) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L15@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2019 = 2.10 (table had 2.28) [user 2026-10-18 A19]; L16@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2019 = 1.60 (table had 1.78) [user 2026-10-18 A19]</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>D1: printed "---" on Air-Way (not applicable to this size) -&gt; cell empty</t>
+          <t>D1: printed "---" on Air-Way (not applicable to this size) -&gt; cell empty | A19 (user 2026-10-18, group 2 settled): L15@DRIVE 2.28 -&gt; OMi 2.10 (Items!L2019, M031) | A19 (user 2026-10-18, group 2 settled): L16@DRIVE 1.78 -&gt; OMi 1.60 (Items!P2019, M032)</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1186,10 +1196,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.26</v>
+        <v>2.14</v>
       </c>
       <c r="C13" t="n">
-        <v>1.7</v>
+        <v>1.58</v>
       </c>
       <c r="D13" t="n">
         <v>1</v>
@@ -1231,7 +1241,12 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Air-Way s101 only (double-pass 20 rows); D1 column printed "---" on most rows (no value) -&gt; cell left empty in table, MISSING for D1 on those rows; CHEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R2020 Hex Flat = 1.000 (table had 1.13) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
+          <t>Air-Way s101 only (double-pass 20 rows); D1 column printed "---" on most rows (no value) -&gt; cell left empty in table, MISSING for D1 on those rows; CHEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R2020 Hex Flat = 1.000 (table had 1.13) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L15@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2020 = 2.14 (table had 2.26) [user 2026-10-18 A19]; L16@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2020 = 1.58 (table had 1.7) [user 2026-10-18 A19]</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>A19 (user 2026-10-18, group 2 settled): L15@DRIVE 2.26 -&gt; OMi 2.14 (Items!L2020, M031) | A19 (user 2026-10-18, group 2 settled): L16@DRIVE 1.7 -&gt; OMi 1.58 (Items!P2020, M032)</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1252,10 +1267,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="C14" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="D14" t="n">
         <v>1.13</v>
@@ -1297,7 +1312,12 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Air-Way s101 only (double-pass 20 rows); D1 column printed "---" on most rows (no value) -&gt; cell left empty in table, MISSING for D1 on those rows</t>
+          <t>Air-Way s101 only (double-pass 20 rows); D1 column printed "---" on most rows (no value) -&gt; cell left empty in table, MISSING for D1 on those rows; L15@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2022 = 2.21 (table had 2.22) [user 2026-10-18 A19]; L16@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2022 = 1.70 (table had 1.72) [user 2026-10-18 A19]</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>A19 (user 2026-10-18, group 2 settled): L15@DRIVE 2.22 -&gt; OMi 2.21 (Items!L2022, M031) | A19 (user 2026-10-18, group 2 settled): L16@DRIVE 1.72 -&gt; OMi 1.70 (Items!P2022, M032)</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1318,10 +1338,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="C15" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="D15" t="n">
         <v>1.13</v>
@@ -1360,12 +1380,12 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Air-Way s101 only (double-pass 20 rows); D1 column printed "---" on most rows (no value) -&gt; cell left empty in table, MISSING for D1 on those rows</t>
+          <t>Air-Way s101 only (double-pass 20 rows); D1 column printed "---" on most rows (no value) -&gt; cell left empty in table, MISSING for D1 on those rows; L15@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2023 = 2.28 (table had 2.26) [user 2026-10-18 A19]; L16@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2023 = 1.72 (table had 1.7) [user 2026-10-18 A19]</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>D1: printed "---" on Air-Way (not applicable to this size) -&gt; cell empty</t>
+          <t>D1: printed "---" on Air-Way (not applicable to this size) -&gt; cell empty | A19 (user 2026-10-18, group 2 settled): L15@DRIVE 2.26 -&gt; OMi 2.28 (Items!L2023, M031) | A19 (user 2026-10-18, group 2 settled): L16@DRIVE 1.7 -&gt; OMi 1.72 (Items!P2023, M032)</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -1386,10 +1406,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="C16" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="D16" t="n">
         <v>1.38</v>
@@ -1431,7 +1451,12 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Air-Way s101 only (double-pass 20 rows); D1 column printed "---" on most rows (no value) -&gt; cell left empty in table, MISSING for D1 on those rows; D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X2024 Side 2 ID = 0.719 (table had 0.84) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
+          <t>Air-Way s101 only (double-pass 20 rows); D1 column printed "---" on most rows (no value) -&gt; cell left empty in table, MISSING for D1 on those rows; D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X2024 Side 2 ID = 0.719 (table had 0.84) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L15@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2024 = 2.38 (table had 2.36) [user 2026-10-18 A19]; L16@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2024 = 1.79 (table had 1.77) [user 2026-10-18 A19]</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>A19 (user 2026-10-18, group 2 settled): L15@DRIVE 2.36 -&gt; OMi 2.38 (Items!L2024, M031) | A19 (user 2026-10-18, group 2 settled): L16@DRIVE 1.77 -&gt; OMi 1.79 (Items!P2024, M032)</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -1489,7 +1514,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1499,7 +1524,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>D1: printed "---" on Air-Way (not applicable to this size) -&gt; cell empty</t>
+          <t>D1: printed "---" on Air-Way (not applicable to this size) -&gt; cell empty | A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on L15@DRIVE=2.56~2.56; L16@DRIVE=1.97~1.97; CHEX@HEX=1.38~1.375; C3HEX@HEX=1.5~1.500; D@BORE=0.84~0.844</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -1586,10 +1611,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.66</v>
+        <v>2.84</v>
       </c>
       <c r="C19" t="n">
-        <v>2.03</v>
+        <v>2.21</v>
       </c>
       <c r="D19" t="n">
         <v>1.69</v>
@@ -1628,12 +1653,12 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Air-Way s101 only (double-pass 20 rows); D1 column printed "---" on most rows (no value) -&gt; cell left empty in table, MISSING for D1 on those rows</t>
+          <t>Air-Way s101 only (double-pass 20 rows); D1 column printed "---" on most rows (no value) -&gt; cell left empty in table, MISSING for D1 on those rows; L15@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2028 = 2.84 (table had 2.66) [user 2026-10-18 A19]; L16@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2028 = 2.21 (table had 2.03) [user 2026-10-18 A19]</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>D1: printed "---" on Air-Way (not applicable to this size) -&gt; cell empty</t>
+          <t>D1: printed "---" on Air-Way (not applicable to this size) -&gt; cell empty | A19 (user 2026-10-18, group 2 settled): L15@DRIVE 2.66 -&gt; OMi 2.84 (Items!L2028, M031) | A19 (user 2026-10-18, group 2 settled): L16@DRIVE 2.03 -&gt; OMi 2.21 (Items!P2028, M032)</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -1720,10 +1745,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="C21" t="n">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="D21" t="n">
         <v>2</v>
@@ -1767,12 +1792,17 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>D1: printed "---" on Air-Way (not applicable to this size) -&gt; cell empty | DROP: Air-Way row with no matching OMi SKU in catalog feed (2026-09-23)</t>
+          <t>D1: printed "---" on Air-Way (not applicable to this size) -&gt; cell empty | DROP: Air-Way row with no matching OMi SKU in catalog feed (2026-09-23) | 2026-10-16: BUILD - the DROP above is void: OMi sells this part, the 2026-09-23 crawl had dropped its SKU | Brennan TFA TFA-p018-t01: agrees on CHEX@HEX, C3HEX@HEX, D@BORE | A19-style (user 2026-10-18 'yes, apply the 7 pending OMi values'): L15@DRIVE 2.94 -&gt; 3.0 | A19-style (user 2026-10-18 'yes, apply the 7 pending OMi values'): L16@DRIVE 2.21 -&gt; 2.27</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>DROP</t>
+          <t>BUILD</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>6505-24-24</t>
         </is>
       </c>
     </row>
@@ -1783,13 +1813,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3.59</v>
+        <v>3.44</v>
       </c>
       <c r="C22" t="n">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="D22" t="n">
-        <v>2.5</v>
+        <v>2.625</v>
       </c>
       <c r="E22" t="n">
         <v>2.88</v>
@@ -1830,12 +1860,17 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>D1: printed "---" on Air-Way (not applicable to this size) -&gt; cell empty | DROP: Air-Way row with no matching OMi SKU in catalog feed (2026-09-23)</t>
+          <t>D1: printed "---" on Air-Way (not applicable to this size) -&gt; cell empty | DROP: Air-Way row with no matching OMi SKU in catalog feed (2026-09-23) | 2026-10-16: BUILD - the DROP above is void: OMi sells this part, the 2026-09-23 crawl had dropped its SKU | OMi dims first (user 2026-09-25): CHEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R2030 = 2.625 (table had 2.5) | Brennan TFA TFA-p018-t01: agrees on CHEX@HEX, C3HEX@HEX, D@BORE | A19-style (user 2026-10-18 'yes, apply the 7 pending OMi values'): L15@DRIVE 3.59 -&gt; 3.44 | A19-style (user 2026-10-18 'yes, apply the 7 pending OMi values'): L16@DRIVE 2.65 -&gt; 2.5</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>DROP</t>
+          <t>BUILD</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>6505-32-32</t>
         </is>
       </c>
     </row>

--- a/04_DESIGN_TABLES/DesignTable_6505.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_6505.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -512,13 +512,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="C3" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="E3" t="n">
         <v>0.5600000000000001</v>
@@ -554,12 +554,12 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Air-Way s101 only (double-pass 20 rows); D1 column printed "---" on most rows (no value) -&gt; cell left empty in table, MISSING for D1 on those rows; CHEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R2009 Hex Flat = 0.500 (table had 0.44) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L15@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2009 = 1.36 (table had 1.34) [user 2026-10-18 A19]; L16@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2009 = 1.01 (table had 1) [user 2026-10-18 A19]</t>
+          <t>Air-Way s101 only (double-pass 20 rows); D1 column printed "---" on most rows (no value) -&gt; cell left empty in table, MISSING for D1 on those rows; CHEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R2009 Hex Flat = 0.500 (table had 0.44) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L15@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2009 = 1.36 (table had 1.34) [user 2026-10-18 A19]; L16@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2009 = 1.01 (table had 1) [user 2026-10-18 A19]; L15@DRIVE: Air-Way 1.34 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.36) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; L16@DRIVE: Air-Way 1 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.01) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; CHEX@HEX: Air-Way 0.44 (raw 07_RAW_EXTRACTS; OMi file / Brennan 0.5) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>D1: printed "---" on Air-Way (not applicable to this size) -&gt; cell empty | A19 (user 2026-10-18, group 2 settled): L15@DRIVE 1.34 -&gt; OMi 1.36 (Items!L2009, M031) | A19 (user 2026-10-18, group 2 settled): L16@DRIVE 1 -&gt; OMi 1.01 (Items!P2009, M032)</t>
+          <t>D1: printed "---" on Air-Way (not applicable to this size) -&gt; cell empty | A19 (user 2026-10-18, group 2 settled): L15@DRIVE 1.34 -&gt; OMi 1.36 (Items!L2009, M031) | A19 (user 2026-10-18, group 2 settled): L16@DRIVE 1 -&gt; OMi 1.01 (Items!P2009, M032) | 2026-10-20 Air-Way first: L15@DRIVE OMi/Brennan 1.36 -&gt; Air-Way 1.34 | 2026-10-20 Air-Way first: L16@DRIVE OMi/Brennan 1.01 -&gt; Air-Way 1 | 2026-10-20 Air-Way first: CHEX@HEX OMi/Brennan 0.5 -&gt; Air-Way 0.44</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -580,10 +580,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="C4" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="D4" t="n">
         <v>0.5600000000000001</v>
@@ -622,12 +622,12 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Air-Way s101 only (double-pass 20 rows); D1 column printed "---" on most rows (no value) -&gt; cell left empty in table, MISSING for D1 on those rows; L15@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2011 = 1.56 (table had 1.53) [user 2026-10-18 A19]; L16@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2011 = 1.21 (table had 1.19) [user 2026-10-18 A19]</t>
+          <t>Air-Way s101 only (double-pass 20 rows); D1 column printed "---" on most rows (no value) -&gt; cell left empty in table, MISSING for D1 on those rows; L15@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2011 = 1.56 (table had 1.53) [user 2026-10-18 A19]; L16@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2011 = 1.21 (table had 1.19) [user 2026-10-18 A19]; L15@DRIVE: Air-Way 1.53 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.56) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; L16@DRIVE: Air-Way 1.19 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.21) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>D1: printed "---" on Air-Way (not applicable to this size) -&gt; cell empty | A19 (user 2026-10-18, group 2 settled): L15@DRIVE 1.53 -&gt; OMi 1.56 (Items!L2011, M031) | A19 (user 2026-10-18, group 2 settled): L16@DRIVE 1.19 -&gt; OMi 1.21 (Items!P2011, M032)</t>
+          <t>D1: printed "---" on Air-Way (not applicable to this size) -&gt; cell empty | A19 (user 2026-10-18, group 2 settled): L15@DRIVE 1.53 -&gt; OMi 1.56 (Items!L2011, M031) | A19 (user 2026-10-18, group 2 settled): L16@DRIVE 1.19 -&gt; OMi 1.21 (Items!P2011, M032) | 2026-10-20 Air-Way first: L15@DRIVE OMi/Brennan 1.56 -&gt; Air-Way 1.53 | 2026-10-20 Air-Way first: L16@DRIVE OMi/Brennan 1.21 -&gt; Air-Way 1.19</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="C5" t="n">
         <v>1.26</v>
@@ -690,12 +690,12 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Air-Way s101 only (double-pass 20 rows); D1 column printed "---" on most rows (no value) -&gt; cell left empty in table, MISSING for D1 on those rows; L15@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2012 = 1.64 (table had 1.63) [user 2026-10-18 A19]</t>
+          <t>Air-Way s101 only (double-pass 20 rows); D1 column printed "---" on most rows (no value) -&gt; cell left empty in table, MISSING for D1 on those rows; L15@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2012 = 1.64 (table had 1.63) [user 2026-10-18 A19]; L15@DRIVE: Air-Way 1.63 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.64) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>D1: printed "---" on Air-Way (not applicable to this size) -&gt; cell empty | A19 (user 2026-10-18, group 2 settled): L15@DRIVE 1.63 -&gt; OMi 1.64 (Items!L2012, M031)</t>
+          <t>D1: printed "---" on Air-Way (not applicable to this size) -&gt; cell empty | A19 (user 2026-10-18, group 2 settled): L15@DRIVE 1.63 -&gt; OMi 1.64 (Items!L2012, M031) | 2026-10-20 Air-Way first: L15@DRIVE OMi/Brennan 1.64 -&gt; Air-Way 1.63</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -716,10 +716,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="C6" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="D6" t="n">
         <v>0.5600000000000001</v>
@@ -761,12 +761,12 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Air-Way s101 only (double-pass 20 rows); D1 column printed "---" on most rows (no value) -&gt; cell left empty in table, MISSING for D1 on those rows; L15@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2013 = 1.68 (table had 1.72) [user 2026-10-18 A19]; L16@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2013 = 1.30 (table had 1.34) [user 2026-10-18 A19]</t>
+          <t>Air-Way s101 only (double-pass 20 rows); D1 column printed "---" on most rows (no value) -&gt; cell left empty in table, MISSING for D1 on those rows; L15@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2013 = 1.68 (table had 1.72) [user 2026-10-18 A19]; L16@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2013 = 1.30 (table had 1.34) [user 2026-10-18 A19]; L15@DRIVE: Air-Way 1.72 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.68) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; L16@DRIVE: Air-Way 1.34 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.3) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>A19 (user 2026-10-18, group 2 settled): L15@DRIVE 1.72 -&gt; OMi 1.68 (Items!L2013, M031) | A19 (user 2026-10-18, group 2 settled): L16@DRIVE 1.34 -&gt; OMi 1.30 (Items!P2013, M032)</t>
+          <t>A19 (user 2026-10-18, group 2 settled): L15@DRIVE 1.72 -&gt; OMi 1.68 (Items!L2013, M031) | A19 (user 2026-10-18, group 2 settled): L16@DRIVE 1.34 -&gt; OMi 1.30 (Items!P2013, M032) | 2026-10-20 Air-Way first: L15@DRIVE OMi/Brennan 1.68 -&gt; Air-Way 1.72 | 2026-10-20 Air-Way first: L16@DRIVE OMi/Brennan 1.3 -&gt; Air-Way 1.34</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -787,10 +787,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.64</v>
+        <v>1.72</v>
       </c>
       <c r="C7" t="n">
-        <v>1.26</v>
+        <v>1.34</v>
       </c>
       <c r="D7" t="n">
         <v>0.75</v>
@@ -829,12 +829,12 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Air-Way s101 only (double-pass 20 rows); D1 column printed "---" on most rows (no value) -&gt; cell left empty in table, MISSING for D1 on those rows; L15@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2015 = 1.64 (table had 1.72) [user 2026-10-18 A19]; L16@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2015 = 1.26 (table had 1.34) [user 2026-10-18 A19]</t>
+          <t>Air-Way s101 only (double-pass 20 rows); D1 column printed "---" on most rows (no value) -&gt; cell left empty in table, MISSING for D1 on those rows; L15@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2015 = 1.64 (table had 1.72) [user 2026-10-18 A19]; L16@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2015 = 1.26 (table had 1.34) [user 2026-10-18 A19]; L15@DRIVE: Air-Way 1.72 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.64) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; L16@DRIVE: Air-Way 1.34 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.26) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>D1: printed "---" on Air-Way (not applicable to this size) -&gt; cell empty | A19 (user 2026-10-18, group 2 settled): L15@DRIVE 1.72 -&gt; OMi 1.64 (Items!L2015, M031) | A19 (user 2026-10-18, group 2 settled): L16@DRIVE 1.34 -&gt; OMi 1.26 (Items!P2015, M032)</t>
+          <t>D1: printed "---" on Air-Way (not applicable to this size) -&gt; cell empty | A19 (user 2026-10-18, group 2 settled): L15@DRIVE 1.72 -&gt; OMi 1.64 (Items!L2015, M031) | A19 (user 2026-10-18, group 2 settled): L16@DRIVE 1.34 -&gt; OMi 1.26 (Items!P2015, M032) | 2026-10-20 Air-Way first: L15@DRIVE OMi/Brennan 1.64 -&gt; Air-Way 1.72 | 2026-10-20 Air-Way first: L16@DRIVE OMi/Brennan 1.26 -&gt; Air-Way 1.34</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -861,7 +861,7 @@
         <v>1.31</v>
       </c>
       <c r="D8" t="n">
-        <v>0.875</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="E8" t="n">
         <v>0.88</v>
@@ -897,12 +897,12 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Air-Way s101 only (double-pass 20 rows); D1 column printed "---" on most rows (no value) -&gt; cell left empty in table, MISSING for D1 on those rows; CHEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R2016 Hex Flat = 0.875 (table had 0.81) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
+          <t>Air-Way s101 only (double-pass 20 rows); D1 column printed "---" on most rows (no value) -&gt; cell left empty in table, MISSING for D1 on those rows; CHEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R2016 Hex Flat = 0.875 (table had 0.81) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; CHEX@HEX: Air-Way 0.81 (raw 07_RAW_EXTRACTS; OMi file / Brennan 0.875) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>D1: printed "---" on Air-Way (not applicable to this size) -&gt; cell empty</t>
+          <t>D1: printed "---" on Air-Way (not applicable to this size) -&gt; cell empty | 2026-10-20 Air-Way first: CHEX@HEX OMi/Brennan 0.875 -&gt; Air-Way 0.81</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -989,10 +989,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="C10" t="n">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="D10" t="n">
         <v>0.88</v>
@@ -1034,12 +1034,12 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Air-Way s101 only (double-pass 20 rows); D1 column printed "---" on most rows (no value) -&gt; cell left empty in table, MISSING for D1 on those rows; L15@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2017 = 1.88 (table had 1.86) [user 2026-10-18 A19]; L16@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2017 = 1.51 (table had 1.48) [user 2026-10-18 A19]</t>
+          <t>Air-Way s101 only (double-pass 20 rows); D1 column printed "---" on most rows (no value) -&gt; cell left empty in table, MISSING for D1 on those rows; L15@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2017 = 1.88 (table had 1.86) [user 2026-10-18 A19]; L16@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2017 = 1.51 (table had 1.48) [user 2026-10-18 A19]; L15@DRIVE: Air-Way 1.86 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.88) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; L16@DRIVE: Air-Way 1.48 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.51) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>A19 (user 2026-10-18, group 2 settled): L15@DRIVE 1.86 -&gt; OMi 1.88 (Items!L2017, M031) | A19 (user 2026-10-18, group 2 settled): L16@DRIVE 1.48 -&gt; OMi 1.51 (Items!P2017, M032)</t>
+          <t>A19 (user 2026-10-18, group 2 settled): L15@DRIVE 1.86 -&gt; OMi 1.88 (Items!L2017, M031) | A19 (user 2026-10-18, group 2 settled): L16@DRIVE 1.48 -&gt; OMi 1.51 (Items!P2017, M032) | 2026-10-20 Air-Way first: L15@DRIVE OMi/Brennan 1.88 -&gt; Air-Way 1.86 | 2026-10-20 Air-Way first: L16@DRIVE OMi/Brennan 1.51 -&gt; Air-Way 1.48</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1060,10 +1060,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="C11" t="n">
-        <v>1.56</v>
+        <v>1.48</v>
       </c>
       <c r="D11" t="n">
         <v>0.88</v>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Air-Way s101 only (double-pass 20 rows); D1 column printed "---" on most rows (no value) -&gt; cell left empty in table, MISSING for D1 on those rows; L15@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2018 = 1.98 (table had 1.9) [user 2026-10-18 A19]; L16@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2018 = 1.56 (table had 1.48) [user 2026-10-18 A19]</t>
+          <t>Air-Way s101 only (double-pass 20 rows); D1 column printed "---" on most rows (no value) -&gt; cell left empty in table, MISSING for D1 on those rows; L15@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2018 = 1.98 (table had 1.9) [user 2026-10-18 A19]; L16@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2018 = 1.56 (table had 1.48) [user 2026-10-18 A19]; L15@DRIVE: Air-Way 1.9 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.98) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; L16@DRIVE: Air-Way 1.48 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.56) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>D1: printed "---" on Air-Way (not applicable to this size) -&gt; cell empty | A19 (user 2026-10-18, group 2 settled): L15@DRIVE 1.9 -&gt; OMi 1.98 (Items!L2018, M031) | A19 (user 2026-10-18, group 2 settled): L16@DRIVE 1.48 -&gt; OMi 1.56 (Items!P2018, M032)</t>
+          <t>D1: printed "---" on Air-Way (not applicable to this size) -&gt; cell empty | A19 (user 2026-10-18, group 2 settled): L15@DRIVE 1.9 -&gt; OMi 1.98 (Items!L2018, M031) | A19 (user 2026-10-18, group 2 settled): L16@DRIVE 1.48 -&gt; OMi 1.56 (Items!P2018, M032) | 2026-10-20 Air-Way first: L15@DRIVE OMi/Brennan 1.98 -&gt; Air-Way 1.9 | 2026-10-20 Air-Way first: L16@DRIVE OMi/Brennan 1.56 -&gt; Air-Way 1.48</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1128,13 +1128,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.1</v>
+        <v>2.28</v>
       </c>
       <c r="C12" t="n">
-        <v>1.6</v>
+        <v>1.78</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E12" t="n">
         <v>1</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Air-Way s101 only (double-pass 20 rows); D1 column printed "---" on most rows (no value) -&gt; cell left empty in table, MISSING for D1 on those rows; CHEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R2019 Hex Flat = 1.000 (table had 0.94) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L15@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2019 = 2.10 (table had 2.28) [user 2026-10-18 A19]; L16@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2019 = 1.60 (table had 1.78) [user 2026-10-18 A19]</t>
+          <t>Air-Way s101 only (double-pass 20 rows); D1 column printed "---" on most rows (no value) -&gt; cell left empty in table, MISSING for D1 on those rows; CHEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R2019 Hex Flat = 1.000 (table had 0.94) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L15@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2019 = 2.10 (table had 2.28) [user 2026-10-18 A19]; L16@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2019 = 1.60 (table had 1.78) [user 2026-10-18 A19]; L15@DRIVE: Air-Way 2.28 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.1) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; L16@DRIVE: Air-Way 1.78 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.6) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; CHEX@HEX: Air-Way 0.94 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>D1: printed "---" on Air-Way (not applicable to this size) -&gt; cell empty | A19 (user 2026-10-18, group 2 settled): L15@DRIVE 2.28 -&gt; OMi 2.10 (Items!L2019, M031) | A19 (user 2026-10-18, group 2 settled): L16@DRIVE 1.78 -&gt; OMi 1.60 (Items!P2019, M032)</t>
+          <t>D1: printed "---" on Air-Way (not applicable to this size) -&gt; cell empty | A19 (user 2026-10-18, group 2 settled): L15@DRIVE 2.28 -&gt; OMi 2.10 (Items!L2019, M031) | A19 (user 2026-10-18, group 2 settled): L16@DRIVE 1.78 -&gt; OMi 1.60 (Items!P2019, M032) | 2026-10-20 Air-Way first: L15@DRIVE OMi/Brennan 2.1 -&gt; Air-Way 2.28 | 2026-10-20 Air-Way first: L16@DRIVE OMi/Brennan 1.6 -&gt; Air-Way 1.78 | 2026-10-20 Air-Way first: CHEX@HEX OMi/Brennan 1 -&gt; Air-Way 0.94</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1196,13 +1196,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.14</v>
+        <v>2.26</v>
       </c>
       <c r="C13" t="n">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="E13" t="n">
         <v>1.25</v>
@@ -1241,12 +1241,12 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Air-Way s101 only (double-pass 20 rows); D1 column printed "---" on most rows (no value) -&gt; cell left empty in table, MISSING for D1 on those rows; CHEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R2020 Hex Flat = 1.000 (table had 1.13) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L15@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2020 = 2.14 (table had 2.26) [user 2026-10-18 A19]; L16@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2020 = 1.58 (table had 1.7) [user 2026-10-18 A19]</t>
+          <t>Air-Way s101 only (double-pass 20 rows); D1 column printed "---" on most rows (no value) -&gt; cell left empty in table, MISSING for D1 on those rows; CHEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R2020 Hex Flat = 1.000 (table had 1.13) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L15@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2020 = 2.14 (table had 2.26) [user 2026-10-18 A19]; L16@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2020 = 1.58 (table had 1.7) [user 2026-10-18 A19]; L15@DRIVE: Air-Way 2.26 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.14) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; L16@DRIVE: Air-Way 1.7 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.58) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; CHEX@HEX: Air-Way 1.13 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>A19 (user 2026-10-18, group 2 settled): L15@DRIVE 2.26 -&gt; OMi 2.14 (Items!L2020, M031) | A19 (user 2026-10-18, group 2 settled): L16@DRIVE 1.7 -&gt; OMi 1.58 (Items!P2020, M032)</t>
+          <t>A19 (user 2026-10-18, group 2 settled): L15@DRIVE 2.26 -&gt; OMi 2.14 (Items!L2020, M031) | A19 (user 2026-10-18, group 2 settled): L16@DRIVE 1.7 -&gt; OMi 1.58 (Items!P2020, M032) | 2026-10-20 Air-Way first: L15@DRIVE OMi/Brennan 2.14 -&gt; Air-Way 2.26 | 2026-10-20 Air-Way first: L16@DRIVE OMi/Brennan 1.58 -&gt; Air-Way 1.7 | 2026-10-20 Air-Way first: CHEX@HEX OMi/Brennan 1 -&gt; Air-Way 1.13</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="C14" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="D14" t="n">
         <v>1.13</v>
@@ -1312,12 +1312,12 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Air-Way s101 only (double-pass 20 rows); D1 column printed "---" on most rows (no value) -&gt; cell left empty in table, MISSING for D1 on those rows; L15@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2022 = 2.21 (table had 2.22) [user 2026-10-18 A19]; L16@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2022 = 1.70 (table had 1.72) [user 2026-10-18 A19]</t>
+          <t>Air-Way s101 only (double-pass 20 rows); D1 column printed "---" on most rows (no value) -&gt; cell left empty in table, MISSING for D1 on those rows; L15@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2022 = 2.21 (table had 2.22) [user 2026-10-18 A19]; L16@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2022 = 1.70 (table had 1.72) [user 2026-10-18 A19]; L15@DRIVE: Air-Way 2.22 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.21) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; L16@DRIVE: Air-Way 1.72 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.7) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>A19 (user 2026-10-18, group 2 settled): L15@DRIVE 2.22 -&gt; OMi 2.21 (Items!L2022, M031) | A19 (user 2026-10-18, group 2 settled): L16@DRIVE 1.72 -&gt; OMi 1.70 (Items!P2022, M032)</t>
+          <t>A19 (user 2026-10-18, group 2 settled): L15@DRIVE 2.22 -&gt; OMi 2.21 (Items!L2022, M031) | A19 (user 2026-10-18, group 2 settled): L16@DRIVE 1.72 -&gt; OMi 1.70 (Items!P2022, M032) | 2026-10-20 Air-Way first: L15@DRIVE OMi/Brennan 2.21 -&gt; Air-Way 2.22 | 2026-10-20 Air-Way first: L16@DRIVE OMi/Brennan 1.7 -&gt; Air-Way 1.72</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1338,10 +1338,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="C15" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="D15" t="n">
         <v>1.13</v>
@@ -1380,12 +1380,12 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Air-Way s101 only (double-pass 20 rows); D1 column printed "---" on most rows (no value) -&gt; cell left empty in table, MISSING for D1 on those rows; L15@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2023 = 2.28 (table had 2.26) [user 2026-10-18 A19]; L16@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2023 = 1.72 (table had 1.7) [user 2026-10-18 A19]</t>
+          <t>Air-Way s101 only (double-pass 20 rows); D1 column printed "---" on most rows (no value) -&gt; cell left empty in table, MISSING for D1 on those rows; L15@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2023 = 2.28 (table had 2.26) [user 2026-10-18 A19]; L16@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2023 = 1.72 (table had 1.7) [user 2026-10-18 A19]; L15@DRIVE: Air-Way 2.26 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.28) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; L16@DRIVE: Air-Way 1.7 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.72) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>D1: printed "---" on Air-Way (not applicable to this size) -&gt; cell empty | A19 (user 2026-10-18, group 2 settled): L15@DRIVE 2.26 -&gt; OMi 2.28 (Items!L2023, M031) | A19 (user 2026-10-18, group 2 settled): L16@DRIVE 1.7 -&gt; OMi 1.72 (Items!P2023, M032)</t>
+          <t>D1: printed "---" on Air-Way (not applicable to this size) -&gt; cell empty | A19 (user 2026-10-18, group 2 settled): L15@DRIVE 2.26 -&gt; OMi 2.28 (Items!L2023, M031) | A19 (user 2026-10-18, group 2 settled): L16@DRIVE 1.7 -&gt; OMi 1.72 (Items!P2023, M032) | 2026-10-20 Air-Way first: L15@DRIVE OMi/Brennan 2.28 -&gt; Air-Way 2.26 | 2026-10-20 Air-Way first: L16@DRIVE OMi/Brennan 1.72 -&gt; Air-Way 1.7</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -1406,10 +1406,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="C16" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="D16" t="n">
         <v>1.38</v>
@@ -1421,7 +1421,7 @@
         <v>0.72</v>
       </c>
       <c r="G16" t="n">
-        <v>0.719</v>
+        <v>0.84</v>
       </c>
       <c r="H16" t="n">
         <v>1.05</v>
@@ -1451,12 +1451,12 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Air-Way s101 only (double-pass 20 rows); D1 column printed "---" on most rows (no value) -&gt; cell left empty in table, MISSING for D1 on those rows; D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X2024 Side 2 ID = 0.719 (table had 0.84) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L15@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2024 = 2.38 (table had 2.36) [user 2026-10-18 A19]; L16@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2024 = 1.79 (table had 1.77) [user 2026-10-18 A19]</t>
+          <t>Air-Way s101 only (double-pass 20 rows); D1 column printed "---" on most rows (no value) -&gt; cell left empty in table, MISSING for D1 on those rows; D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X2024 Side 2 ID = 0.719 (table had 0.84) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L15@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2024 = 2.38 (table had 2.36) [user 2026-10-18 A19]; L16@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2024 = 1.79 (table had 1.77) [user 2026-10-18 A19]; L15@DRIVE: Air-Way 2.36 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.38) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; L16@DRIVE: Air-Way 1.77 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.79) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; D@BORE: Air-Way 0.84 (raw 07_RAW_EXTRACTS; OMi file / Brennan 0.719) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>A19 (user 2026-10-18, group 2 settled): L15@DRIVE 2.36 -&gt; OMi 2.38 (Items!L2024, M031) | A19 (user 2026-10-18, group 2 settled): L16@DRIVE 1.77 -&gt; OMi 1.79 (Items!P2024, M032)</t>
+          <t>A19 (user 2026-10-18, group 2 settled): L15@DRIVE 2.36 -&gt; OMi 2.38 (Items!L2024, M031) | A19 (user 2026-10-18, group 2 settled): L16@DRIVE 1.77 -&gt; OMi 1.79 (Items!P2024, M032) | 2026-10-20 Air-Way first: L15@DRIVE OMi/Brennan 2.38 -&gt; Air-Way 2.36 | 2026-10-20 Air-Way first: L16@DRIVE OMi/Brennan 1.79 -&gt; Air-Way 1.77 | 2026-10-20 Air-Way first: D@BORE OMi/Brennan 0.719 -&gt; Air-Way 0.84</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -1611,10 +1611,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.84</v>
+        <v>2.66</v>
       </c>
       <c r="C19" t="n">
-        <v>2.21</v>
+        <v>2.03</v>
       </c>
       <c r="D19" t="n">
         <v>1.69</v>
@@ -1653,12 +1653,12 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Air-Way s101 only (double-pass 20 rows); D1 column printed "---" on most rows (no value) -&gt; cell left empty in table, MISSING for D1 on those rows; L15@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2028 = 2.84 (table had 2.66) [user 2026-10-18 A19]; L16@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2028 = 2.21 (table had 2.03) [user 2026-10-18 A19]</t>
+          <t>Air-Way s101 only (double-pass 20 rows); D1 column printed "---" on most rows (no value) -&gt; cell left empty in table, MISSING for D1 on those rows; L15@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2028 = 2.84 (table had 2.66) [user 2026-10-18 A19]; L16@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P2028 = 2.21 (table had 2.03) [user 2026-10-18 A19]; L15@DRIVE: Air-Way 2.66 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.84) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; L16@DRIVE: Air-Way 2.03 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.21) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>D1: printed "---" on Air-Way (not applicable to this size) -&gt; cell empty | A19 (user 2026-10-18, group 2 settled): L15@DRIVE 2.66 -&gt; OMi 2.84 (Items!L2028, M031) | A19 (user 2026-10-18, group 2 settled): L16@DRIVE 2.03 -&gt; OMi 2.21 (Items!P2028, M032)</t>
+          <t>D1: printed "---" on Air-Way (not applicable to this size) -&gt; cell empty | A19 (user 2026-10-18, group 2 settled): L15@DRIVE 2.66 -&gt; OMi 2.84 (Items!L2028, M031) | A19 (user 2026-10-18, group 2 settled): L16@DRIVE 2.03 -&gt; OMi 2.21 (Items!P2028, M032) | 2026-10-20 Air-Way first: L15@DRIVE OMi/Brennan 2.84 -&gt; Air-Way 2.66 | 2026-10-20 Air-Way first: L16@DRIVE OMi/Brennan 2.21 -&gt; Air-Way 2.03</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -1745,10 +1745,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="C21" t="n">
-        <v>2.27</v>
+        <v>2.21</v>
       </c>
       <c r="D21" t="n">
         <v>2</v>
@@ -1787,12 +1787,12 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Air-Way s101 only (double-pass 20 rows); D1 column printed "---" on most rows (no value) -&gt; cell left empty in table, MISSING for D1 on those rows</t>
+          <t>Air-Way s101 only (double-pass 20 rows); D1 column printed "---" on most rows (no value) -&gt; cell left empty in table, MISSING for D1 on those rows; L15@DRIVE: Air-Way 2.94 (raw 07_RAW_EXTRACTS; OMi file / Brennan 3) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; L16@DRIVE: Air-Way 2.21 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.27) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>D1: printed "---" on Air-Way (not applicable to this size) -&gt; cell empty | DROP: Air-Way row with no matching OMi SKU in catalog feed (2026-09-23) | 2026-10-16: BUILD - the DROP above is void: OMi sells this part, the 2026-09-23 crawl had dropped its SKU | Brennan TFA TFA-p018-t01: agrees on CHEX@HEX, C3HEX@HEX, D@BORE | A19-style (user 2026-10-18 'yes, apply the 7 pending OMi values'): L15@DRIVE 2.94 -&gt; 3.0 | A19-style (user 2026-10-18 'yes, apply the 7 pending OMi values'): L16@DRIVE 2.21 -&gt; 2.27</t>
+          <t>D1: printed "---" on Air-Way (not applicable to this size) -&gt; cell empty | DROP: Air-Way row with no matching OMi SKU in catalog feed (2026-09-23) | 2026-10-16: BUILD - the DROP above is void: OMi sells this part, the 2026-09-23 crawl had dropped its SKU | Brennan TFA TFA-p018-t01: agrees on CHEX@HEX, C3HEX@HEX, D@BORE | A19-style (user 2026-10-18 'yes, apply the 7 pending OMi values'): L15@DRIVE 2.94 -&gt; 3.0 | A19-style (user 2026-10-18 'yes, apply the 7 pending OMi values'): L16@DRIVE 2.21 -&gt; 2.27 | 2026-10-20 Air-Way first: L15@DRIVE OMi/Brennan 3 -&gt; Air-Way 2.94 | 2026-10-20 Air-Way first: L16@DRIVE OMi/Brennan 2.27 -&gt; Air-Way 2.21</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -1813,13 +1813,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3.44</v>
+        <v>3.59</v>
       </c>
       <c r="C22" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="D22" t="n">
         <v>2.5</v>
-      </c>
-      <c r="D22" t="n">
-        <v>2.625</v>
       </c>
       <c r="E22" t="n">
         <v>2.88</v>
@@ -1855,12 +1855,12 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Air-Way s101 only (double-pass 20 rows); D1 column printed "---" on most rows (no value) -&gt; cell left empty in table, MISSING for D1 on those rows</t>
+          <t>Air-Way s101 only (double-pass 20 rows); D1 column printed "---" on most rows (no value) -&gt; cell left empty in table, MISSING for D1 on those rows; L15@DRIVE: Air-Way 3.59 (raw 07_RAW_EXTRACTS; OMi file / Brennan 3.44) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; L16@DRIVE: Air-Way 2.65 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.5) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; CHEX@HEX: Air-Way 2.5 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.625) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>D1: printed "---" on Air-Way (not applicable to this size) -&gt; cell empty | DROP: Air-Way row with no matching OMi SKU in catalog feed (2026-09-23) | 2026-10-16: BUILD - the DROP above is void: OMi sells this part, the 2026-09-23 crawl had dropped its SKU | OMi dims first (user 2026-09-25): CHEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R2030 = 2.625 (table had 2.5) | Brennan TFA TFA-p018-t01: agrees on CHEX@HEX, C3HEX@HEX, D@BORE | A19-style (user 2026-10-18 'yes, apply the 7 pending OMi values'): L15@DRIVE 3.59 -&gt; 3.44 | A19-style (user 2026-10-18 'yes, apply the 7 pending OMi values'): L16@DRIVE 2.65 -&gt; 2.5</t>
+          <t>D1: printed "---" on Air-Way (not applicable to this size) -&gt; cell empty | DROP: Air-Way row with no matching OMi SKU in catalog feed (2026-09-23) | 2026-10-16: BUILD - the DROP above is void: OMi sells this part, the 2026-09-23 crawl had dropped its SKU | OMi dims first (user 2026-09-25): CHEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R2030 = 2.625 (table had 2.5) | Brennan TFA TFA-p018-t01: agrees on CHEX@HEX, C3HEX@HEX, D@BORE | A19-style (user 2026-10-18 'yes, apply the 7 pending OMi values'): L15@DRIVE 3.59 -&gt; 3.44 | A19-style (user 2026-10-18 'yes, apply the 7 pending OMi values'): L16@DRIVE 2.65 -&gt; 2.5 | 2026-10-20 Air-Way first: L15@DRIVE OMi/Brennan 3.44 -&gt; Air-Way 3.59 | 2026-10-20 Air-Way first: L16@DRIVE OMi/Brennan 2.5 -&gt; Air-Way 2.65 | 2026-10-20 Air-Way first: CHEX@HEX OMi/Brennan 2.625 -&gt; Air-Way 2.5</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
